--- a/output/pdf_financials_xlsx/CTN.xlsx
+++ b/output/pdf_financials_xlsx/CTN.xlsx
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003136</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
         <v>-0.280875</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.420431</v>
+        <v>-2.423567</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.686461</v>
@@ -2178,7 +2178,7 @@
         <v>-0.280729</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.419975</v>
+        <v>-2.423111</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.685202</v>
@@ -2478,43 +2478,43 @@
         <v>0.009350000000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001113</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004764</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004226</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.17316</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.02035</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003847</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.335235</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001348</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000713</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.013312</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.009868999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000776</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.00271</v>
       </c>
     </row>
     <row r="35">
@@ -2594,43 +2594,43 @@
         <v>0.009350000000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001113</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.004764</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004226</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.17316</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.02035</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003847</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.335235</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001348</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000713</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.013312</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.009868999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000776</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.00271</v>
       </c>
     </row>
     <row r="37">
@@ -3290,43 +3290,43 @@
         <v>0.037303</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.008358000000000001</v>
+        <v>0.007245</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.014198</v>
+        <v>0.009434</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.006977</v>
+        <v>0.002751</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.272466</v>
+        <v>0.09930600000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.096716</v>
+        <v>0.076366</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.018308</v>
+        <v>0.014461</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.5974</v>
+        <v>0.262165</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.003185</v>
+        <v>0.001837</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.006426</v>
+        <v>0.005713</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.020075</v>
+        <v>0.006763</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.015583</v>
+        <v>0.005714</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.00649</v>
+        <v>0.005714</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.007922999999999999</v>
+        <v>0.005213</v>
       </c>
     </row>
     <row r="49">
@@ -7786,10 +7786,10 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032835</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.037968</v>
       </c>
       <c r="O124" s="3" t="n">
         <v>0</v>
@@ -7798,10 +7798,10 @@
         <v>0</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.068116</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.050154</v>
       </c>
     </row>
     <row r="125">
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032835</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.037968</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -7856,10 +7856,10 @@
         <v>0</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.068116</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.050154</v>
       </c>
     </row>
     <row r="126">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22064,7 +22064,11 @@
           <t>Lease payments 4</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -23515,7 +23519,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -26099,7 +26107,11 @@
           <t>Lease payments 5</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -41267,7 +41279,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -61962,7 +61974,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">

--- a/output/pdf_financials_xlsx/CTN.xlsx
+++ b/output/pdf_financials_xlsx/CTN.xlsx
@@ -804,10 +804,10 @@
         <v>0.012385</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.047382</v>
+        <v>0.125291</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.029128</v>
+        <v>0.076224</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.280875</v>
+        <v>-0.281876</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.420431</v>
+        <v>-2.390389</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-3.686461</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.001001</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.030042</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.280875</v>
+        <v>-0.281876</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.423567</v>
+        <v>-2.393525</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.686461</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.280729</v>
+        <v>-0.28173</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.423111</v>
+        <v>-2.393069</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.685202</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.3551206913678355</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.25678289182221</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4423,19 +4423,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0225</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -23624,7 +23624,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -39384,7 +39388,11 @@
           <t>Recovery of rent and office expenses 4, 10</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -62483,7 +62491,11 @@
           <t>Future income tax recovery (expense) (Note 8)</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E544" s="5" t="n">
         <v>-0.001001</v>
       </c>
